--- a/Output/PowerPoint_Figures/Fig_7/Fig_7e_data.xlsx
+++ b/Output/PowerPoint_Figures/Fig_7/Fig_7e_data.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,139 +418,139 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Cumulative_Coefficients</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Bortezomib</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Cobimetinib</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Daunorubicin</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Doxorubicin</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Epirubicin</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Ibrutinib</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Ibuprofen</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Isoproterenol</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Mexiletine</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Panobinostat</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Rosiglitazone</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Sotalol</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Sunitinib</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Vandetanib</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Vioxx</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Amiodarone</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Chlorpromazine</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Gemcitibine</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Nifedipine</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Vincristine</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Vorinostat</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Dactinomycin</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Erlotinib</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Etomoxir</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Plicamycin</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>k_elim_Contractility</t>
         </is>
@@ -644,7 +632,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>k_elim_Contractility + kappa_O2</t>
         </is>
@@ -726,7 +714,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>k_elim_Contractility + kappa_O2 + R0_Contractility</t>
         </is>
@@ -808,7 +796,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>k_elim_Contractility + kappa_O2 + R0_Contractility + k_elim_O2</t>
         </is>
@@ -890,7 +878,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>k_elim_Contractility + kappa_O2 + R0_Contractility + k_elim_O2 + Emax_Contractility</t>
         </is>
@@ -972,7 +960,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>k_elim_Contractility + kappa_O2 + R0_Contractility + k_elim_O2 + Emax_Contractility + tau_O2</t>
         </is>
@@ -1054,7 +1042,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>k_elim_Contractility + kappa_O2 + R0_Contractility + k_elim_O2 + Emax_Contractility + tau_O2 + m_Contractility</t>
         </is>
@@ -1136,7 +1124,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>k_elim_Contractility + kappa_O2 + R0_Contractility + k_elim_O2 + Emax_Contractility + tau_O2 + m_Contractility + Emax_O2</t>
         </is>
@@ -1218,7 +1206,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>k_elim_Contractility + kappa_O2 + R0_Contractility + k_elim_O2 + Emax_Contractility + tau_O2 + m_Contractility + Emax_O2 + m_O2</t>
         </is>
@@ -1300,7 +1288,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>k_elim_Contractility + kappa_O2 + R0_Contractility + k_elim_O2 + Emax_Contractility + tau_O2 + m_Contractility + Emax_O2 + m_O2 + R0_O2</t>
         </is>
@@ -1382,7 +1370,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>k_elim_Contractility + kappa_O2 + R0_Contractility + k_elim_O2 + Emax_Contractility + tau_O2 + m_Contractility + Emax_O2 + m_O2 + R0_O2 + kappa_Contractility</t>
         </is>
@@ -1464,7 +1452,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>k_elim_Contractility + kappa_O2 + R0_Contractility + k_elim_O2 + Emax_Contractility + tau_O2 + m_Contractility + Emax_O2 + m_O2 + R0_O2 + kappa_Contractility + tau_Contractility</t>
         </is>
@@ -1546,7 +1534,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>k_elim_Contractility + kappa_O2 + R0_Contractility + k_elim_O2 + Emax_Contractility + tau_O2 + m_Contractility + Emax_O2 + m_O2 + R0_O2 + kappa_Contractility + tau_Contractility + n_O2</t>
         </is>
@@ -1628,7 +1616,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>k_elim_Contractility + kappa_O2 + R0_Contractility + k_elim_O2 + Emax_Contractility + tau_O2 + m_Contractility + Emax_O2 + m_O2 + R0_O2 + kappa_Contractility + tau_Contractility + n_O2 + n_Contractility</t>
         </is>
@@ -1724,34 +1712,34 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Source_File</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Threshold</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Threshold_Source</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Label_Source</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Cumulative_Plot_Data\heart_damage_cumulative_predictions.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Cumulative_Plot_Data/heart_damage_cumulative_predictions.csv</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1759,12 +1747,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\prediction_thresholds.json</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/prediction_thresholds.json</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\heart_damage_predictions.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/heart_damage_predictions.csv</t>
         </is>
       </c>
     </row>
